--- a/sheets/민요/검수/밀양 아리랑.xlsx
+++ b/sheets/민요/검수/밀양 아리랑.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,66 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4544,8 +4683,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U28"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4568,1321 +4711,1512 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밀양 아리랑 — 민요채보-2/밀양 아리랑.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">밀양 아리랑</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">섣</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">좀</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">좀</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="21"/>
+      <c r="L4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 仲</t>
         </is>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="M4" s="21"/>
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="R4" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U4" s="21"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="22"/>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="22"/>
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좀</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="O5" s="22"/>
+      <c r="P5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="S5" s="22"/>
+      <c r="T5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">본</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="20"/>
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q6" s="20"/>
+      <c r="R6" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="U6" s="20"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">듯</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">一
 無</t>
         </is>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="23"/>
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="R7" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S7" s="21"/>
+      <c r="T7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="U7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="22"/>
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좀</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="22"/>
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="N8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="O8" s="22"/>
+      <c r="P8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="S8" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="U8" s="22"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="17"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="20"/>
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="K9" s="20"/>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="O9" s="20"/>
+      <c r="P9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="Q9" s="20"/>
+      <c r="R9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="T9" s="17"/>
+      <c r="U9" s="20"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="17"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">보</t>
         </is>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="J10" s="17"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M10" s="21"/>
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="O10" s="21"/>
+      <c r="P10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="S10" s="21"/>
+      <c r="T10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="U10" s="21"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="17"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="J11" s="17"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="M11" s="22"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q11" s="22"/>
+      <c r="R11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="S11" s="22"/>
+      <c r="T11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="U11" s="22"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="17"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="I12" s="20"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="Q12" s="20"/>
+      <c r="R12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="S12" s="20"/>
+      <c r="T12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="I13" s="21"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑
 仲</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="Q13" s="21"/>
+      <c r="R13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="S13" s="21"/>
+      <c r="T13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="U13" s="21"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="17"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="I14" s="22"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="Q14" s="22"/>
+      <c r="R14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밀양 아리랑 — 민요채보-2/밀양 아리랑.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="S14" s="22"/>
+      <c r="T14" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U14" s="22"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">밀양 아리랑</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="19"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="S17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="T17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="U17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="19"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 ○</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="S18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="T18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="U18" s="21"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="19"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="S19" s="22"/>
+      <c r="T19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="U19" s="22"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="19"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="S20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="T20" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U20" s="20"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="19"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="S21" s="21"/>
+      <c r="T21" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="U21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="19"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="S22" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="T22" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="U22" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="19"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S23" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="T23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="U23" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="19"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="S24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="T24" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="U24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="19"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="S25" s="22"/>
+      <c r="T25" s="17"/>
+      <c r="U25" s="22"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="19"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="S26" s="20"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="20"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="19"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="S27" s="21"/>
+      <c r="T27" s="17"/>
+      <c r="U27" s="21"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="19"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/밀양 아리랑.xlsx
+++ b/sheets/민요/검수/밀양 아리랑.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|―</t>
+          <t xml:space="preserve">仲|–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="2"/>
@@ -944,12 +944,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I19" s="2"/>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1796,12 +1796,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -2825,12 +2825,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4024,12 +4024,12 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4131,12 +4131,12 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4348,12 +4348,12 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4525,12 +4525,12 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I113" s="2"/>
@@ -4847,7 +4847,7 @@
       <c r="R5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="S5" s="10"/>
@@ -4926,28 +4926,28 @@
       <c r="A7" s="0"/>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
       <c r="G7" s="9"/>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4960,28 +4960,28 @@
       <c r="K7" s="9"/>
       <c r="L7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
       <c r="Q7" s="9"/>
       <c r="R7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -5130,7 +5130,7 @@
       <c r="C10" s="9"/>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5155,21 +5155,21 @@
       <c r="K10" s="9"/>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
       <c r="O10" s="9"/>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -5251,7 +5251,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="8"/>
@@ -5275,7 +5275,7 @@
       <c r="I12" s="8"/>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K12" s="8"/>
@@ -5300,7 +5300,7 @@
       <c r="Q12" s="8"/>
       <c r="R12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5318,14 +5318,14 @@
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5344,14 +5344,14 @@
       <c r="K13" s="9"/>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -5428,7 +5428,7 @@
       <c r="Q14" s="10"/>
       <c r="R14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S14" s="10"/>

--- a/sheets/민요/검수/밀양 아리랑.xlsx
+++ b/sheets/민요/검수/밀양 아리랑.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4643,797 +4696,797 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">밀양 아리랑</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I3" s="22"/>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K3" s="22"/>
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="M3" s="22"/>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O3" s="22"/>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S3" s="8"/>
-      <c r="T3" s="18" t="inlineStr">
+      <c r="S3" s="22"/>
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">^</t>
         </is>
       </c>
-      <c r="U3" s="11"/>
+      <c r="U3" s="24"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="M4" s="25"/>
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="18" t="inlineStr">
+      <c r="Q4" s="25"/>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S4" s="25"/>
+      <c r="T4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U4" s="12"/>
+      <c r="U4" s="26"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="27"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="27"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="I5" s="27"/>
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="28"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="27"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="27"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="Q5" s="27"/>
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –</t>
         </is>
       </c>
-      <c r="S5" s="10"/>
-      <c r="T5" s="19" t="inlineStr">
+      <c r="S5" s="27"/>
+      <c r="T5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="U5" s="16"/>
+      <c r="U5" s="30"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="C6" s="24"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="22"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="22"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="18" t="inlineStr">
+      <c r="M6" s="22"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O6" s="22"/>
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="Q6" s="11"/>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="Q6" s="24"/>
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S6" s="8"/>
-      <c r="T6" s="19" t="inlineStr">
+      <c r="S6" s="22"/>
+      <c r="T6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="U6" s="14"/>
+      <c r="U6" s="31"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="25"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="25"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="M7" s="25"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="25"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="Q7" s="25"/>
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="S7" s="9"/>
-      <c r="T7" s="19" t="inlineStr">
+      <c r="S7" s="25"/>
+      <c r="T7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="U7" s="15"/>
+      <c r="U7" s="32"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="C8" s="27"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="27"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="I8" s="27"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K8" s="27"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M8" s="27"/>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O8" s="27"/>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S8" s="10"/>
-      <c r="T8" s="19" t="inlineStr">
+      <c r="S8" s="27"/>
+      <c r="T8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="U8" s="16"/>
+      <c r="U8" s="30"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="22"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="K9" s="22"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O9" s="8"/>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="M9" s="22"/>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O9" s="22"/>
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="Q9" s="22"/>
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S9" s="8"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="8"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="25"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="E10" s="25"/>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="25"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="25"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="Q10" s="25"/>
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S10" s="9"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="9"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="27"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="I11" s="27"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K11" s="27"/>
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="M11" s="27"/>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S11" s="10"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="10"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S11" s="27"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="27"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M12" s="22"/>
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="O12" s="22"/>
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="17" t="inlineStr">
+      <c r="Q12" s="22"/>
+      <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S12" s="8"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="8"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17" t="inlineStr">
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="S13" s="9"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="9"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="M14" s="27"/>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O14" s="27"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17" t="inlineStr">
+      <c r="Q14" s="27"/>
+      <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="10"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/밀양 아리랑.xlsx
+++ b/sheets/민요/검수/밀양 아리랑.xlsx
@@ -4669,32 +4669,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4800,37 +4800,37 @@
       <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="25"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="25"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K4" s="25"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M4" s="25"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="25"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q4" s="25"/>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="U4" s="26"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4857,19 +4857,19 @@
       <c r="C5" s="27"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="27"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="27"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="27"/>
@@ -4881,13 +4881,13 @@
       <c r="K5" s="28"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="27"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="27"/>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="U5" s="30"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K6" s="22"/>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="U6" s="31"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="U7" s="32"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="U8" s="30"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
       <c r="O14" s="27"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q14" s="27"/>

--- a/sheets/민요/검수/밀양 아리랑.xlsx
+++ b/sheets/민요/검수/밀양 아리랑.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -248,6 +253,33 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4728,61 +4760,61 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="33"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="33"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="33"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="22"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K3" s="22"/>
+      <c r="K3" s="33"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="22"/>
+      <c r="M3" s="33"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O3" s="22"/>
+      <c r="O3" s="33"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q3" s="22"/>
+      <c r="Q3" s="33"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S3" s="22"/>
+      <c r="S3" s="33"/>
       <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">^</t>
         </is>
       </c>
-      <c r="U3" s="24"/>
+      <c r="U3" s="34"/>
     </row>
     <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
@@ -4791,61 +4823,61 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="35"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="35"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="35"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K4" s="25"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="35"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="25"/>
+      <c r="O4" s="35"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q4" s="25"/>
+      <c r="Q4" s="35"/>
       <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S4" s="25"/>
+      <c r="S4" s="35"/>
       <c r="T4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U4" s="26"/>
+      <c r="U4" s="36"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -4854,62 +4886,62 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="37"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="37"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="27"/>
+      <c r="I5" s="37"/>
       <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K5" s="28"/>
+      <c r="K5" s="38"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="27"/>
+      <c r="M5" s="37"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="27"/>
+      <c r="O5" s="37"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q5" s="27"/>
+      <c r="Q5" s="37"/>
       <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 –</t>
         </is>
       </c>
-      <c r="S5" s="27"/>
+      <c r="S5" s="37"/>
       <c r="T5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="U5" s="30"/>
+      <c r="U5" s="39"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -4919,61 +4951,61 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="24"/>
+      <c r="C6" s="34"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="33"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="22"/>
+      <c r="K6" s="33"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M6" s="22"/>
+      <c r="M6" s="33"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O6" s="22"/>
+      <c r="O6" s="33"/>
       <c r="P6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="Q6" s="24"/>
+      <c r="Q6" s="34"/>
       <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S6" s="22"/>
+      <c r="S6" s="33"/>
       <c r="T6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="U6" s="31"/>
+      <c r="U6" s="40"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -4983,68 +5015,68 @@
 無</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="E7" s="25"/>
+      <c r="E7" s="35"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G7" s="25"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="35"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="35"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="M7" s="25"/>
+      <c r="M7" s="35"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="O7" s="25"/>
+      <c r="O7" s="35"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="Q7" s="25"/>
+      <c r="Q7" s="35"/>
       <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="S7" s="25"/>
+      <c r="S7" s="35"/>
       <c r="T7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="U7" s="32"/>
+      <c r="U7" s="41"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -5053,64 +5085,64 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="37"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="37"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="37"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="37"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="27"/>
+      <c r="K8" s="37"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M8" s="27"/>
+      <c r="M8" s="37"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O8" s="27"/>
+      <c r="O8" s="37"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q8" s="27"/>
+      <c r="Q8" s="37"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S8" s="27"/>
+      <c r="S8" s="37"/>
       <c r="T8" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="U8" s="30"/>
+      <c r="U8" s="39"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -5119,58 +5151,58 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="33"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="22"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="33"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K9" s="22"/>
+      <c r="K9" s="33"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="22"/>
+      <c r="M9" s="33"/>
       <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="33"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q9" s="22"/>
+      <c r="Q9" s="33"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="S9" s="22"/>
+      <c r="S9" s="33"/>
       <c r="T9" s="21"/>
-      <c r="U9" s="22"/>
+      <c r="U9" s="33"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -5180,62 +5212,62 @@
 姑</t>
         </is>
       </c>
-      <c r="C10" s="25"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E10" s="25"/>
+      <c r="E10" s="35"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I10" s="25"/>
+      <c r="I10" s="35"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K10" s="25"/>
+      <c r="K10" s="35"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="M10" s="25"/>
+      <c r="M10" s="35"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="O10" s="25"/>
+      <c r="O10" s="35"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="Q10" s="25"/>
+      <c r="Q10" s="35"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S10" s="25"/>
+      <c r="S10" s="35"/>
       <c r="T10" s="21"/>
-      <c r="U10" s="25"/>
+      <c r="U10" s="35"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -5244,61 +5276,61 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="37"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E11" s="27"/>
+      <c r="E11" s="37"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="37"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="27"/>
+      <c r="K11" s="37"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M11" s="27"/>
+      <c r="M11" s="37"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O11" s="27"/>
+      <c r="O11" s="37"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="27"/>
+      <c r="Q11" s="37"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S11" s="27"/>
+      <c r="S11" s="37"/>
       <c r="T11" s="21"/>
-      <c r="U11" s="27"/>
+      <c r="U11" s="37"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -5307,59 +5339,59 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="33"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="33"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="33"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="33"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="22"/>
+      <c r="M12" s="33"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O12" s="22"/>
+      <c r="O12" s="33"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q12" s="22"/>
+      <c r="Q12" s="33"/>
       <c r="R12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S12" s="22"/>
+      <c r="S12" s="33"/>
       <c r="T12" s="21"/>
-      <c r="U12" s="22"/>
+      <c r="U12" s="33"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -5368,62 +5400,62 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="35"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="35"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="35"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="O13" s="25"/>
+      <c r="O13" s="35"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="35"/>
       <c r="R13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="S13" s="25"/>
+      <c r="S13" s="35"/>
       <c r="T13" s="21"/>
-      <c r="U13" s="25"/>
+      <c r="U13" s="35"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -5432,61 +5464,61 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="37"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="37"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="37"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="37"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="37"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O14" s="27"/>
+      <c r="O14" s="37"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q14" s="27"/>
+      <c r="Q14" s="37"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S14" s="27"/>
+      <c r="S14" s="37"/>
       <c r="T14" s="21"/>
-      <c r="U14" s="27"/>
+      <c r="U14" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/밀양 아리랑.xlsx
+++ b/sheets/민요/검수/밀양 아리랑.xlsx
@@ -537,10 +537,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/밀양 아리랑.xlsx
+++ b/sheets/민요/검수/밀양 아리랑.xlsx
@@ -430,24 +430,8 @@
 본</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-–</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+    <t xml:space="preserve">無
+–㴌</t>
   </si>
   <si>
     <t xml:space="preserve">아
@@ -478,17 +462,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -610,7 +594,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -668,6 +652,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2622,332 +2650,332 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="60.61" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="19" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="19" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="22" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B11" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="23" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B12" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="19" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B13" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="22"/>
+      <c r="D13" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="22"/>
+      <c r="F13" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="22"/>
+      <c r="H13" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="22" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="9" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B14" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="23"/>
+      <c r="H14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="23" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2957,7 +2985,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/밀양 아리랑.xlsx
+++ b/sheets/민요/검수/밀양 아리랑.xlsx
@@ -2656,13 +2656,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
   </cols>
   <sheetData>
